--- a/tests/fixtures/bow-923/结营评审表.xlsx
+++ b/tests/fixtures/bow-923/结营评审表.xlsx
@@ -381,16 +381,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-01</x:v>
       </x:c>
       <x:c r="F2" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>任辞远（演示）</x:v>
       </x:c>
       <x:c r="G2" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -399,7 +399,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
@@ -413,16 +413,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E3" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-01</x:v>
       </x:c>
       <x:c r="F3" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>任辞远（演示）</x:v>
       </x:c>
       <x:c r="G3" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H3" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -431,7 +431,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -445,16 +445,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E4" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-01</x:v>
       </x:c>
       <x:c r="F4" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>任辞远（演示）</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -463,7 +463,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J4" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
@@ -480,13 +480,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E5" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-01</x:v>
       </x:c>
       <x:c r="F5" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>任辞远（演示）</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H5" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -512,13 +512,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E6" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-01</x:v>
       </x:c>
       <x:c r="F6" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>任辞远（演示）</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H6" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -540,18 +540,26 @@
       <x:c r="C7" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3"/>
-      <x:c r="F7" s="3"/>
-      <x:c r="G7" s="10"/>
+      <x:c r="D7" s="3" t="str">
+        <x:v>建议留用</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>s-29</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
+        <x:v>孟砚舟（演示）</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="n">
+        <x:v>46265.25</x:v>
+      </x:c>
       <x:c r="H7" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>缺段</x:v>
+        <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -565,16 +573,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D8" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E8" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F8" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -583,7 +591,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>演示重建：本次仅记录替代课题的演示配合，未评价入营作品所涉任务。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -597,16 +605,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D9" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E9" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F9" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H9" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -615,7 +623,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -629,16 +637,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D10" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E10" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F10" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H10" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -647,7 +655,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J10" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -661,16 +669,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D11" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E11" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F11" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -679,7 +687,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -696,13 +704,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E12" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F12" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G12" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -724,18 +732,26 @@
       <x:c r="C13" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D13" s="3"/>
-      <x:c r="E13" s="3"/>
-      <x:c r="F13" s="3"/>
-      <x:c r="G13" s="10"/>
+      <x:c r="D13" s="3" t="str">
+        <x:v>不建议</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>s-29</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>孟砚舟（演示）</x:v>
+      </x:c>
+      <x:c r="G13" s="10" t="n">
+        <x:v>46265.25</x:v>
+      </x:c>
       <x:c r="H13" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I13" s="3" t="str">
-        <x:v>缺段</x:v>
+        <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
@@ -749,16 +765,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D14" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E14" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F14" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G14" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H14" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -767,7 +783,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J14" s="3" t="str">
-        <x:v>演示重建：本次仅记录替代课题的演示配合，未评价入营作品所涉任务。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -781,16 +797,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D15" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E15" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F15" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G15" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H15" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -799,7 +815,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J15" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -812,18 +828,26 @@
       <x:c r="C16" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D16" s="3"/>
-      <x:c r="E16" s="3"/>
-      <x:c r="F16" s="3"/>
-      <x:c r="G16" s="10"/>
+      <x:c r="D16" s="3" t="str">
+        <x:v>继续观察</x:v>
+      </x:c>
+      <x:c r="E16" s="3" t="str">
+        <x:v>s-29</x:v>
+      </x:c>
+      <x:c r="F16" s="3" t="str">
+        <x:v>孟砚舟（演示）</x:v>
+      </x:c>
+      <x:c r="G16" s="10" t="n">
+        <x:v>46265.25</x:v>
+      </x:c>
       <x:c r="H16" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I16" s="3" t="str">
-        <x:v>缺段</x:v>
+        <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J16" s="3" t="str">
-        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
+        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -837,16 +861,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D17" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E17" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-24</x:v>
       </x:c>
       <x:c r="F17" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>严朝夕（演示）</x:v>
       </x:c>
       <x:c r="G17" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H17" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -855,7 +879,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -869,16 +893,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D18" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E18" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-24</x:v>
       </x:c>
       <x:c r="F18" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>严朝夕（演示）</x:v>
       </x:c>
       <x:c r="G18" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H18" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -887,7 +911,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -901,16 +925,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D19" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E19" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-24</x:v>
       </x:c>
       <x:c r="F19" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>严朝夕（演示）</x:v>
       </x:c>
       <x:c r="G19" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H19" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -919,7 +943,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J19" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -936,13 +960,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E20" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-24</x:v>
       </x:c>
       <x:c r="F20" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>严朝夕（演示）</x:v>
       </x:c>
       <x:c r="G20" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H20" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -965,16 +989,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D21" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E21" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-24</x:v>
       </x:c>
       <x:c r="F21" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>严朝夕（演示）</x:v>
       </x:c>
       <x:c r="G21" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H21" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -983,7 +1007,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J21" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -997,16 +1021,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D22" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E22" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-24</x:v>
       </x:c>
       <x:c r="F22" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>严朝夕（演示）</x:v>
       </x:c>
       <x:c r="G22" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H22" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1015,7 +1039,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J22" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -1029,16 +1053,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D23" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E23" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-27</x:v>
       </x:c>
       <x:c r="F23" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>祁清和（演示）</x:v>
       </x:c>
       <x:c r="G23" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H23" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1047,7 +1071,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J23" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -1061,16 +1085,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D24" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E24" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-27</x:v>
       </x:c>
       <x:c r="F24" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>祁清和（演示）</x:v>
       </x:c>
       <x:c r="G24" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1079,7 +1103,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J24" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -1092,26 +1116,18 @@
       <x:c r="C25" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D25" s="3" t="str">
-        <x:v>建议留用</x:v>
-      </x:c>
-      <x:c r="E25" s="3" t="str">
-        <x:v>s-28</x:v>
-      </x:c>
-      <x:c r="F25" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
-      </x:c>
-      <x:c r="G25" s="10" t="n">
-        <x:v>46185.25</x:v>
-      </x:c>
+      <x:c r="D25" s="3"/>
+      <x:c r="E25" s="3"/>
+      <x:c r="F25" s="3"/>
+      <x:c r="G25" s="10"/>
       <x:c r="H25" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I25" s="3" t="str">
-        <x:v>已确认（演示）</x:v>
+        <x:v>缺段</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -1125,16 +1141,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D26" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E26" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-27</x:v>
       </x:c>
       <x:c r="F26" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>祁清和（演示）</x:v>
       </x:c>
       <x:c r="G26" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H26" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1143,7 +1159,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -1160,13 +1176,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E27" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-27</x:v>
       </x:c>
       <x:c r="F27" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>祁清和（演示）</x:v>
       </x:c>
       <x:c r="G27" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H27" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1189,16 +1205,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D28" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E28" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F28" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G28" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1207,7 +1223,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J28" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -1221,16 +1237,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D29" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E29" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F29" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G29" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H29" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1239,7 +1255,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J29" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -1253,16 +1269,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D30" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E30" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F30" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G30" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H30" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1271,7 +1287,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J30" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -1288,13 +1304,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E31" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F31" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G31" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H31" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1317,16 +1333,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D32" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E32" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F32" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G32" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H32" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1335,7 +1351,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J32" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="48" customHeight="1">
@@ -1349,16 +1365,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D33" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E33" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F33" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G33" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H33" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1367,7 +1383,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J33" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="48" customHeight="1">
@@ -1381,16 +1397,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D34" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E34" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F34" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G34" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H34" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1399,7 +1415,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J34" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="48" customHeight="1">
@@ -1413,16 +1429,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D35" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E35" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F35" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G35" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H35" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1431,7 +1447,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J35" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="48" customHeight="1">
@@ -1448,13 +1464,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E36" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F36" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G36" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H36" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1477,16 +1493,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D37" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E37" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F37" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G37" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H37" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1495,7 +1511,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J37" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="48" customHeight="1">
@@ -1512,13 +1528,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E38" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-22</x:v>
       </x:c>
       <x:c r="F38" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>萧静姝（演示）</x:v>
       </x:c>
       <x:c r="G38" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H38" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1541,16 +1557,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D39" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E39" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F39" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G39" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H39" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1559,7 +1575,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J39" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="48" customHeight="1">
@@ -1576,13 +1592,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E40" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F40" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G40" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H40" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1608,13 +1624,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E41" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F41" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G41" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H41" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1640,13 +1656,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E42" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F42" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G42" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H42" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1669,16 +1685,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D43" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E43" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F43" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G43" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H43" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1687,7 +1703,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J43" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：营内转到另一方向的课题，结营评审针对新方向的任务。</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="48" customHeight="1">
@@ -1704,13 +1720,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E44" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F44" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G44" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H44" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1736,13 +1752,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E45" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F45" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G45" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H45" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1768,13 +1784,13 @@
         <x:v>不建议</x:v>
       </x:c>
       <x:c r="E46" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F46" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G46" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H46" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1797,16 +1813,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D47" s="3" t="str">
-        <x:v>不建议</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E47" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-04</x:v>
       </x:c>
       <x:c r="F47" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜安歌（演示）</x:v>
       </x:c>
       <x:c r="G47" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H47" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1815,7 +1831,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J47" s="3" t="str">
-        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="48" customHeight="1">
@@ -1832,13 +1848,13 @@
         <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E48" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F48" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G48" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H48" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1861,16 +1877,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D49" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E49" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F49" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G49" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H49" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1879,7 +1895,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J49" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="48" customHeight="1">
@@ -1893,16 +1909,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D50" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E50" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F50" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G50" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H50" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1911,7 +1927,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J50" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="48" customHeight="1">
@@ -1925,16 +1941,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D51" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E51" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F51" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G51" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H51" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -1943,7 +1959,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J51" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="48" customHeight="1">
@@ -1956,26 +1972,18 @@
       <x:c r="C52" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D52" s="3" t="str">
-        <x:v>继续观察</x:v>
-      </x:c>
-      <x:c r="E52" s="3" t="str">
-        <x:v>s-28</x:v>
-      </x:c>
-      <x:c r="F52" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
-      </x:c>
-      <x:c r="G52" s="10" t="n">
-        <x:v>46185.25</x:v>
-      </x:c>
+      <x:c r="D52" s="3"/>
+      <x:c r="E52" s="3"/>
+      <x:c r="F52" s="3"/>
+      <x:c r="G52" s="10"/>
       <x:c r="H52" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I52" s="3" t="str">
-        <x:v>已确认（演示）</x:v>
+        <x:v>缺段</x:v>
       </x:c>
       <x:c r="J52" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="48" customHeight="1">
@@ -1989,16 +1997,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D53" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E53" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F53" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G53" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H53" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2007,7 +2015,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J53" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="48" customHeight="1">
@@ -2021,16 +2029,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D54" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E54" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F54" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G54" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H54" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2039,7 +2047,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J54" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="48" customHeight="1">
@@ -2053,16 +2061,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D55" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E55" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F55" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G55" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H55" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2071,7 +2079,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J55" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="48" customHeight="1">
@@ -2088,13 +2096,13 @@
         <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E56" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F56" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G56" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H56" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2117,16 +2125,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D57" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E57" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-10</x:v>
       </x:c>
       <x:c r="F57" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>杜南乔（演示）</x:v>
       </x:c>
       <x:c r="G57" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H57" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2135,7 +2143,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J57" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="48" customHeight="1">
@@ -2149,16 +2157,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D58" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E58" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F58" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G58" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H58" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2167,7 +2175,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J58" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="48" customHeight="1">
@@ -2181,16 +2189,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D59" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E59" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F59" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G59" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H59" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2199,7 +2207,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J59" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="48" customHeight="1">
@@ -2213,16 +2221,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D60" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E60" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F60" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G60" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H60" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2231,7 +2239,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J60" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="48" customHeight="1">
@@ -2248,13 +2256,13 @@
         <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E61" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F61" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G61" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H61" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2277,16 +2285,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D62" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E62" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F62" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G62" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H62" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2295,7 +2303,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J62" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
@@ -2309,16 +2317,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D63" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E63" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F63" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G63" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H63" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2327,7 +2335,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J63" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="48" customHeight="1">
@@ -2341,16 +2349,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D64" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E64" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F64" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G64" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H64" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2359,7 +2367,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J64" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="48" customHeight="1">
@@ -2376,13 +2384,13 @@
         <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E65" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F65" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G65" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H65" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2405,16 +2413,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D66" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E66" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F66" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G66" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H66" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2423,7 +2431,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J66" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="48" customHeight="1">
@@ -2437,16 +2445,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D67" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E67" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-15</x:v>
       </x:c>
       <x:c r="F67" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>邱行之（演示）</x:v>
       </x:c>
       <x:c r="G67" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H67" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2455,7 +2463,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J67" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="48" customHeight="1">
@@ -2469,16 +2477,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D68" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E68" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F68" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G68" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H68" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2487,7 +2495,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J68" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="48" customHeight="1">
@@ -2501,16 +2509,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D69" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E69" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F69" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G69" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H69" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2519,7 +2527,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J69" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="48" customHeight="1">
@@ -2532,26 +2540,18 @@
       <x:c r="C70" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D70" s="3" t="str">
-        <x:v>继续观察</x:v>
-      </x:c>
-      <x:c r="E70" s="3" t="str">
-        <x:v>s-28</x:v>
-      </x:c>
-      <x:c r="F70" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
-      </x:c>
-      <x:c r="G70" s="10" t="n">
-        <x:v>46185.25</x:v>
-      </x:c>
+      <x:c r="D70" s="3"/>
+      <x:c r="E70" s="3"/>
+      <x:c r="F70" s="3"/>
+      <x:c r="G70" s="10"/>
       <x:c r="H70" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I70" s="3" t="str">
-        <x:v>已确认（演示）</x:v>
+        <x:v>缺段</x:v>
       </x:c>
       <x:c r="J70" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="48" customHeight="1">
@@ -2565,16 +2565,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D71" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E71" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F71" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G71" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H71" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2583,7 +2583,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J71" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="48" customHeight="1">
@@ -2600,13 +2600,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E72" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F72" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G72" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H72" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2629,16 +2629,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D73" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E73" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F73" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G73" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H73" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2647,7 +2647,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J73" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="48" customHeight="1">
@@ -2661,16 +2661,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D74" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E74" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F74" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G74" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H74" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2679,7 +2679,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J74" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="48" customHeight="1">
@@ -2696,13 +2696,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E75" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F75" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G75" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H75" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2728,13 +2728,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E76" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F76" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G76" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H76" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2757,16 +2757,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D77" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E77" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F77" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G77" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H77" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2775,7 +2775,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J77" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="48" customHeight="1">
@@ -2792,13 +2792,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E78" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F78" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G78" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H78" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2821,16 +2821,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D79" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E79" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F79" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G79" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H79" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2839,7 +2839,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J79" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="48" customHeight="1">
@@ -2853,16 +2853,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D80" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E80" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F80" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G80" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H80" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2871,7 +2871,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J80" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="48" customHeight="1">
@@ -2888,13 +2888,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E81" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F81" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G81" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H81" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2917,16 +2917,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D82" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E82" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-06</x:v>
       </x:c>
       <x:c r="F82" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>彭若溪（演示）</x:v>
       </x:c>
       <x:c r="G82" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H82" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2935,7 +2935,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J82" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="48" customHeight="1">
@@ -2952,13 +2952,13 @@
         <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E83" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F83" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G83" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H83" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2981,16 +2981,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D84" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>继续观察</x:v>
       </x:c>
       <x:c r="E84" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F84" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G84" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H84" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -2999,7 +2999,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J84" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="48" customHeight="1">
@@ -3013,16 +3013,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D85" s="3" t="str">
-        <x:v>建议留用</x:v>
+        <x:v>不建议</x:v>
       </x:c>
       <x:c r="E85" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F85" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G85" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H85" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -3031,7 +3031,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J85" s="3" t="str">
-        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
+        <x:v>演示重建：营内独立交付多次未闭合，复盘未给出可复现的改进证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="48" customHeight="1">
@@ -3045,16 +3045,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D86" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E86" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-29</x:v>
       </x:c>
       <x:c r="F86" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>孟砚舟（演示）</x:v>
       </x:c>
       <x:c r="G86" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H86" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -3063,7 +3063,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J86" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="48" customHeight="1">
@@ -3077,16 +3077,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D87" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E87" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-19</x:v>
       </x:c>
       <x:c r="F87" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>贺望舒（演示）</x:v>
       </x:c>
       <x:c r="G87" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H87" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -3095,7 +3095,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J87" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="48" customHeight="1">
@@ -3109,16 +3109,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D88" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E88" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-19</x:v>
       </x:c>
       <x:c r="F88" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>贺望舒（演示）</x:v>
       </x:c>
       <x:c r="G88" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H88" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -3127,7 +3127,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J88" s="3" t="str">
-        <x:v>演示重建：能在明确任务下交付，独立拆解与跨环节协作仍需继续观察。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="48" customHeight="1">
@@ -3140,18 +3140,26 @@
       <x:c r="C89" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D89" s="3"/>
-      <x:c r="E89" s="3"/>
-      <x:c r="F89" s="3"/>
-      <x:c r="G89" s="10"/>
+      <x:c r="D89" s="3" t="str">
+        <x:v>建议留用</x:v>
+      </x:c>
+      <x:c r="E89" s="3" t="str">
+        <x:v>s-19</x:v>
+      </x:c>
+      <x:c r="F89" s="3" t="str">
+        <x:v>贺望舒（演示）</x:v>
+      </x:c>
+      <x:c r="G89" s="10" t="n">
+        <x:v>46265.25</x:v>
+      </x:c>
       <x:c r="H89" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I89" s="3" t="str">
-        <x:v>缺段</x:v>
+        <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J89" s="3" t="str">
-        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="48" customHeight="1">
@@ -3164,18 +3172,26 @@
       <x:c r="C90" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D90" s="3"/>
-      <x:c r="E90" s="3"/>
-      <x:c r="F90" s="3"/>
-      <x:c r="G90" s="10"/>
+      <x:c r="D90" s="3" t="str">
+        <x:v>建议留用</x:v>
+      </x:c>
+      <x:c r="E90" s="3" t="str">
+        <x:v>s-19</x:v>
+      </x:c>
+      <x:c r="F90" s="3" t="str">
+        <x:v>贺望舒（演示）</x:v>
+      </x:c>
+      <x:c r="G90" s="10" t="n">
+        <x:v>46265.25</x:v>
+      </x:c>
       <x:c r="H90" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I90" s="3" t="str">
-        <x:v>缺段</x:v>
+        <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J90" s="3" t="str">
-        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="48" customHeight="1">
@@ -3212,18 +3228,26 @@
       <x:c r="C92" s="3" t="str">
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
-      <x:c r="D92" s="3"/>
-      <x:c r="E92" s="3"/>
-      <x:c r="F92" s="3"/>
-      <x:c r="G92" s="10"/>
+      <x:c r="D92" s="3" t="str">
+        <x:v>建议留用</x:v>
+      </x:c>
+      <x:c r="E92" s="3" t="str">
+        <x:v>s-19</x:v>
+      </x:c>
+      <x:c r="F92" s="3" t="str">
+        <x:v>贺望舒（演示）</x:v>
+      </x:c>
+      <x:c r="G92" s="10" t="n">
+        <x:v>46265.25</x:v>
+      </x:c>
       <x:c r="H92" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
       </x:c>
       <x:c r="I92" s="3" t="str">
-        <x:v>缺段</x:v>
+        <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J92" s="3" t="str">
-        <x:v>演示重建：缺少结营评审记录，未补造评价或评价人。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="48" customHeight="1">
@@ -3237,16 +3261,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D93" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E93" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-19</x:v>
       </x:c>
       <x:c r="F93" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>贺望舒（演示）</x:v>
       </x:c>
       <x:c r="G93" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H93" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -3255,7 +3279,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J93" s="3" t="str">
-        <x:v>演示重建：本次仅记录替代课题的演示配合，未评价入营作品所涉任务。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="48" customHeight="1">
@@ -3269,16 +3293,16 @@
         <x:v>XEngineer 第六期（演示）</x:v>
       </x:c>
       <x:c r="D94" s="3" t="str">
-        <x:v>继续观察</x:v>
+        <x:v>建议留用</x:v>
       </x:c>
       <x:c r="E94" s="3" t="str">
-        <x:v>s-28</x:v>
+        <x:v>s-19</x:v>
       </x:c>
       <x:c r="F94" s="3" t="str">
-        <x:v>许致远（演示）</x:v>
+        <x:v>贺望舒（演示）</x:v>
       </x:c>
       <x:c r="G94" s="10" t="n">
-        <x:v>46185.25</x:v>
+        <x:v>46265.25</x:v>
       </x:c>
       <x:c r="H94" s="3" t="str">
         <x:v>demo-xe-graduation-three-bands-v1</x:v>
@@ -3287,7 +3311,7 @@
         <x:v>已确认（演示）</x:v>
       </x:c>
       <x:c r="J94" s="3" t="str">
-        <x:v>演示重建：本次仅记录替代课题的演示配合，未评价入营作品所涉任务。</x:v>
+        <x:v>演示重建：能独立闭合任务，复盘给出可复现步骤，并帮助同伴定位一次故障。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
